--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-02-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£12.15</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£15.26</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£15.86</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.71</t>
+          <t>£19.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.71</t>
+          <t>£19.70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.71</t>
+          <t>£19.70</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.75</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -993,19 +993,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>£22.05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>£22.05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>£22.50</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>£22.50</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>£22.50</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>£22.95</t>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.06</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£22.11</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.09</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.09</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.09</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£25.47</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1269,34 +1269,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£27.67</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£27.67</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£27.67</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£28.25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£27.43</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>£27.69</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>£27.69</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£27.69</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£28.25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>£27.43</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£27.69</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>POA</t>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£27.69</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>£27.22</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>£27.22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£27.22</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£27.95</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>£27.24</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>£27.25</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>£27.25</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£27.25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£27.95</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>£27.24</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£27.25</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>POA</t>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>£32.40</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>£32.40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>£32.40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£33.83</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£33.83</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£33.83</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£33.38</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£41.61</t>
+          <t>£39.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£41.61</t>
+          <t>£39.42</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£41.61</t>
+          <t>£39.42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£40.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£42.85</t>
+          <t>£40.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.85</t>
+          <t>£40.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£42.35</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1821,34 +1821,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>£40.49</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>£40.49</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>£40.49</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>£40.50</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>£40.68</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>£40.68</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>£40.68</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>£41.50</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>£40.50</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>£40.68</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>POA</t>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£40.68</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>£745.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>£745.00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>£745.00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>£765.00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>£765.00</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>£765.00</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>£765.00</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>N/L</t>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£779.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2005,24 +2005,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>£935.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>£935.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>£935.00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>£985.00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>£985.00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>£985.00</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>£985.00</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>£1407.24</t>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£1019.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£28.53</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£28.53</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£28.53</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£28.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2373,17 +2373,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£42.55</t>
+          <t>£40.55</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£42.55</t>
+          <t>£40.55</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£42.55</t>
+          <t>£40.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£42.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£47.45</t>
+          <t>£44.80</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£47.45</t>
+          <t>£44.80</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£47.45</t>
+          <t>£44.80</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£48.17</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£45.40</t>
+          <t>£43.65</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£45.40</t>
+          <t>£43.65</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£45.40</t>
+          <t>£43.65</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£47.58</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£1,016.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£47.08</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1267.2</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
